--- a/data/gravel/Panorama Taiga EXP 2 2025.xlsx
+++ b/data/gravel/Panorama Taiga EXP 2 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/hardtail/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DC7B5B5-8361-2748-B97D-3D0C198ED444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36D8C16C-4778-094E-A245-03FD8B219329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4020" yWindow="3000" windowWidth="24780" windowHeight="15000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -344,7 +344,7 @@
     <t> (100mm SUSPENSION FORK EQUIVALENT AT 25% SAG)</t>
   </si>
   <si>
-    <t>us</t>
+    <t>USD</t>
   </si>
 </sst>
 </file>

--- a/data/gravel/Panorama Taiga EXP 2 2025.xlsx
+++ b/data/gravel/Panorama Taiga EXP 2 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36D8C16C-4778-094E-A245-03FD8B219329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{854F1C6C-8896-4040-84B7-FA892F223CA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4020" yWindow="3000" windowWidth="24780" windowHeight="15000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="105">
   <si>
     <t>brand</t>
   </si>
@@ -345,6 +345,9 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>https://www.panoramacycles.com/cdn/shop/files/taiga-exp-2-501891.jpg?v=1732295839</t>
   </si>
 </sst>
 </file>
@@ -737,6 +740,11 @@
         <v>79</v>
       </c>
     </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>104</v>
+      </c>
+    </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>

--- a/data/gravel/Panorama Taiga EXP 2 2025.xlsx
+++ b/data/gravel/Panorama Taiga EXP 2 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{854F1C6C-8896-4040-84B7-FA892F223CA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83FCED5B-5A0B-3D40-B569-712119F63FFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4020" yWindow="3000" windowWidth="24780" windowHeight="15000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="107">
   <si>
     <t>brand</t>
   </si>
@@ -348,6 +348,12 @@
   </si>
   <si>
     <t>https://www.panoramacycles.com/cdn/shop/files/taiga-exp-2-501891.jpg?v=1732295839</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Granby, Québec, Canada</t>
   </si>
 </sst>
 </file>
@@ -694,7 +700,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1445,6 +1451,14 @@
         <v>103</v>
       </c>
     </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>105</v>
+      </c>
+      <c r="B73" t="s">
+        <v>106</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Panorama Taiga EXP 2 2025.xlsx
+++ b/data/gravel/Panorama Taiga EXP 2 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83FCED5B-5A0B-3D40-B569-712119F63FFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAD0B4FD-1477-DE4A-98F0-B433AE48F644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4020" yWindow="3000" windowWidth="24780" windowHeight="15000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="108">
   <si>
     <t>brand</t>
   </si>
@@ -354,6 +354,9 @@
   </si>
   <si>
     <t>Granby, Québec, Canada</t>
+  </si>
+  <si>
+    <t>internal</t>
   </si>
 </sst>
 </file>
@@ -1352,6 +1355,9 @@
       <c r="A59" t="s">
         <v>55</v>
       </c>
+      <c r="B59" s="1" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
@@ -1370,24 +1376,24 @@
       <c r="A62" t="s">
         <v>58</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>70</v>
+      <c r="B62" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>59</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>70</v>
+      <c r="B63" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>60</v>
       </c>
-      <c r="B64" s="1" t="s">
-        <v>70</v>
+      <c r="B64" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">

--- a/data/gravel/Panorama Taiga EXP 2 2025.xlsx
+++ b/data/gravel/Panorama Taiga EXP 2 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAD0B4FD-1477-DE4A-98F0-B433AE48F644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03B13999-3F7B-D241-8844-8894C7DEADC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4020" yWindow="3000" windowWidth="24780" windowHeight="15000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="114">
   <si>
     <t>brand</t>
   </si>
@@ -357,6 +357,24 @@
   </si>
   <si>
     <t>internal</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -703,7 +721,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1289,124 +1307,109 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>45</v>
-      </c>
-      <c r="B49" s="1"/>
+        <v>108</v>
+      </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>46</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>47</v>
-      </c>
-      <c r="B51">
-        <v>27.2</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>48</v>
-      </c>
-      <c r="B52" s="1"/>
+        <v>111</v>
+      </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>49</v>
-      </c>
-      <c r="B53">
-        <v>42</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>50</v>
+        <v>113</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>51</v>
-      </c>
-      <c r="B55">
-        <v>180</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B55" s="1"/>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>52</v>
-      </c>
-      <c r="B56">
-        <v>160</v>
+        <v>46</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>53</v>
+        <v>47</v>
+      </c>
+      <c r="B57">
+        <v>27.2</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>54</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="B58" s="1"/>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>55</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>107</v>
+        <v>49</v>
+      </c>
+      <c r="B59">
+        <v>42</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>56</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>57</v>
+        <v>51</v>
+      </c>
+      <c r="B61">
+        <v>180</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>58</v>
-      </c>
-      <c r="B62" s="1">
-        <v>2</v>
+        <v>52</v>
+      </c>
+      <c r="B62">
+        <v>160</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>59</v>
-      </c>
-      <c r="B63" s="1">
-        <v>1</v>
+        <v>53</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>60</v>
-      </c>
-      <c r="B64" s="1">
-        <v>1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>70</v>
@@ -1414,54 +1417,99 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>63</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>64</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>70</v>
+        <v>58</v>
+      </c>
+      <c r="B68" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>65</v>
-      </c>
-      <c r="B69">
-        <v>1349</v>
+        <v>59</v>
+      </c>
+      <c r="B69" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>66</v>
-      </c>
-      <c r="B70">
-        <v>3149</v>
+        <v>60</v>
+      </c>
+      <c r="B70" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>67</v>
+        <v>61</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>63</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>64</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>65</v>
+      </c>
+      <c r="B75">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>66</v>
+      </c>
+      <c r="B76">
+        <v>3149</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>68</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>105</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B79" t="s">
         <v>106</v>
       </c>
     </row>

--- a/data/gravel/Panorama Taiga EXP 2 2025.xlsx
+++ b/data/gravel/Panorama Taiga EXP 2 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03B13999-3F7B-D241-8844-8894C7DEADC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F869DF7-2A82-2B44-BBE6-51237CEBCBD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4020" yWindow="3000" windowWidth="24780" windowHeight="15000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="116">
   <si>
     <t>brand</t>
   </si>
@@ -338,9 +338,6 @@
     <t>450-465</t>
   </si>
   <si>
-    <t>a8:e32</t>
-  </si>
-  <si>
     <t> (100mm SUSPENSION FORK EQUIVALENT AT 25% SAG)</t>
   </si>
   <si>
@@ -375,6 +372,15 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>a8:e34</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
   </si>
 </sst>
 </file>
@@ -721,7 +727,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -769,7 +775,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -777,7 +783,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1063,406 +1069,416 @@
         <v>480</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>22</v>
-      </c>
-      <c r="F25">
-        <f>505 - 0.25*100</f>
-        <v>480</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>23</v>
-      </c>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="21" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25" s="3"/>
+    </row>
+    <row r="26" spans="1:8" ht="21" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>26</v>
-      </c>
-      <c r="C28">
-        <v>700</v>
-      </c>
-      <c r="D28">
-        <v>700</v>
-      </c>
-      <c r="E28">
-        <v>700</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>26</v>
+      </c>
+      <c r="C30">
+        <v>700</v>
+      </c>
+      <c r="D30">
+        <v>700</v>
+      </c>
+      <c r="E30">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>27</v>
       </c>
-      <c r="C29">
+      <c r="C31">
         <f>2.2*25.4</f>
         <v>55.88</v>
       </c>
-      <c r="D29">
-        <f t="shared" ref="D29:E29" si="0">2.2*25.4</f>
+      <c r="D31">
+        <f t="shared" ref="D31:E31" si="0">2.2*25.4</f>
         <v>55.88</v>
       </c>
-      <c r="E29">
+      <c r="E31">
         <f t="shared" si="0"/>
         <v>55.88</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>28</v>
       </c>
-      <c r="C30">
+      <c r="C32">
         <f>2.6*25.4</f>
         <v>66.039999999999992</v>
       </c>
-      <c r="D30">
+      <c r="D32">
         <f>2.6*25.4</f>
         <v>66.039999999999992</v>
       </c>
-      <c r="E30">
+      <c r="E32">
         <f>2.6*25.4</f>
         <v>66.039999999999992</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>29</v>
       </c>
-      <c r="C31">
-        <f>C33*2.54</f>
+      <c r="C33">
+        <f>C35*2.54</f>
         <v>162.56</v>
       </c>
-      <c r="D31">
-        <f t="shared" ref="D31:E32" si="1">D33*2.54</f>
+      <c r="D33">
+        <f t="shared" ref="D33:E34" si="1">D35*2.54</f>
         <v>172.72</v>
       </c>
-      <c r="E31">
+      <c r="E33">
         <f t="shared" si="1"/>
         <v>180.34</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>30</v>
       </c>
-      <c r="C32">
-        <f>C34*2.54</f>
+      <c r="C34">
+        <f>C36*2.54</f>
         <v>172.72</v>
       </c>
-      <c r="D32">
+      <c r="D34">
         <f t="shared" si="1"/>
         <v>180.34</v>
       </c>
-      <c r="E32">
+      <c r="E34">
         <f t="shared" si="1"/>
         <v>190.5</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C33">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C35">
         <v>64</v>
       </c>
-      <c r="D33">
+      <c r="D35">
         <v>68</v>
       </c>
-      <c r="E33">
+      <c r="E35">
         <v>71</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>31</v>
-      </c>
-      <c r="B34" t="s">
-        <v>32</v>
-      </c>
-      <c r="C34">
-        <v>68</v>
-      </c>
-      <c r="D34">
-        <v>71</v>
-      </c>
-      <c r="E34">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>71</v>
-      </c>
-      <c r="B35" t="s">
-        <v>72</v>
-      </c>
-      <c r="C35" t="s">
-        <v>83</v>
-      </c>
-      <c r="D35" t="s">
-        <v>84</v>
-      </c>
-      <c r="E35" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="B36" t="s">
-        <v>74</v>
+        <v>32</v>
+      </c>
+      <c r="C36">
+        <v>68</v>
+      </c>
+      <c r="D36">
+        <v>71</v>
+      </c>
+      <c r="E36">
+        <v>75</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>75</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>76</v>
+        <v>71</v>
+      </c>
+      <c r="B37" t="s">
+        <v>72</v>
+      </c>
+      <c r="C37" t="s">
+        <v>83</v>
+      </c>
+      <c r="D37" t="s">
+        <v>84</v>
+      </c>
+      <c r="E37" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="B38" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>36</v>
+        <v>33</v>
+      </c>
+      <c r="B40" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>35</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>37</v>
       </c>
-      <c r="B41">
+      <c r="B43">
         <f>2.6*25.4</f>
         <v>66.039999999999992</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>38</v>
-      </c>
-      <c r="B42" s="1">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>39</v>
-      </c>
-      <c r="B43">
-        <v>100</v>
-      </c>
-    </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>40</v>
+        <v>38</v>
+      </c>
+      <c r="B44" s="1">
+        <v>2.8</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>39</v>
+      </c>
+      <c r="B45">
+        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>43</v>
-      </c>
-      <c r="B47">
-        <v>148</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>44</v>
-      </c>
-      <c r="B48">
-        <v>110</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>108</v>
+        <v>43</v>
+      </c>
+      <c r="B49">
+        <v>148</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>109</v>
+        <v>44</v>
+      </c>
+      <c r="B50">
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>45</v>
-      </c>
-      <c r="B55" s="1"/>
+        <v>111</v>
+      </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>46</v>
+        <v>112</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>47</v>
-      </c>
-      <c r="B57">
-        <v>27.2</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B57" s="1"/>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>48</v>
-      </c>
-      <c r="B58" s="1"/>
+        <v>46</v>
+      </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B59">
-        <v>42</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>50</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="B60" s="1"/>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B61">
-        <v>180</v>
+        <v>42</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>52</v>
-      </c>
-      <c r="B62">
-        <v>160</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>53</v>
+        <v>51</v>
+      </c>
+      <c r="B63">
+        <v>180</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>54</v>
+        <v>52</v>
+      </c>
+      <c r="B64">
+        <v>160</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>55</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>107</v>
+        <v>53</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>56</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>57</v>
+        <v>55</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>58</v>
-      </c>
-      <c r="B68" s="1">
-        <v>2</v>
+        <v>56</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>59</v>
-      </c>
-      <c r="B69" s="1">
-        <v>1</v>
+        <v>57</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B70" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>61</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>70</v>
+        <v>59</v>
+      </c>
+      <c r="B71" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>62</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>70</v>
+        <v>60</v>
+      </c>
+      <c r="B72" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>70</v>
@@ -1470,7 +1486,7 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>70</v>
@@ -1478,39 +1494,55 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>65</v>
-      </c>
-      <c r="B75">
-        <v>1349</v>
+        <v>63</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>66</v>
-      </c>
-      <c r="B76">
-        <v>3149</v>
+        <v>64</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>67</v>
+        <v>65</v>
+      </c>
+      <c r="B77">
+        <v>1349</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>68</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>103</v>
+        <v>66</v>
+      </c>
+      <c r="B78">
+        <v>3149</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>68</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>104</v>
+      </c>
+      <c r="B81" t="s">
         <v>105</v>
-      </c>
-      <c r="B79" t="s">
-        <v>106</v>
       </c>
     </row>
   </sheetData>
